--- a/backend/data/uploads/MES/2026-07-08_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-08_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1EC6CD7-5232-4AB0-9DB7-7A07F58AF86E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E244A449-D220-4393-8A3A-17C054C55947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{5F444540-84A4-40AB-A8DF-6011586AA8B3}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{60D005C6-5C0C-439B-94AE-C2A5C9D0A915}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{449675A7-5A13-45F3-9509-34122B2A6887}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7E8CC7C-D44C-403D-8715-501DE8EDC4D2}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-08_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-08_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E244A449-D220-4393-8A3A-17C054C55947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDE6A310-6E14-4390-AEFE-97D90B75FD6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{60D005C6-5C0C-439B-94AE-C2A5C9D0A915}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{E1DC4D93-3708-4002-998B-0CFFEF5D3A4C}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7E8CC7C-D44C-403D-8715-501DE8EDC4D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{880336C2-21D1-493C-A2E7-1B16721AF050}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-08_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-08_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDE6A310-6E14-4390-AEFE-97D90B75FD6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2695F354-3056-435D-9E99-2DE6AE28EAC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{E1DC4D93-3708-4002-998B-0CFFEF5D3A4C}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{5B020368-C770-4C39-95A6-E063343C14FE}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{880336C2-21D1-493C-A2E7-1B16721AF050}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0795CFBF-EBDE-483E-893E-C90DC2AA1008}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
